--- a/js/data/Antarctic_Territorial_Claims_clean.xlsx
+++ b/js/data/Antarctic_Territorial_Claims_clean.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jab14\OneDrive\Documents\school 2026\FIT2179\A2\js\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jab14\OneDrive\Documents\GitHub\FIT2179_A2\js\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7A9AA8-EFE2-49CB-BB8F-08D2207BD989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647BA95E-756C-4B6E-BFDD-27A7DF69A7AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4700" yWindow="3110" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>Territory</t>
   </si>
@@ -39,48 +39,27 @@
     <t>(District of the French Southern and Antarctic Lands)</t>
   </si>
   <si>
-    <t> France</t>
-  </si>
-  <si>
     <t>Argentine Antarctica</t>
   </si>
   <si>
-    <t> Argentina</t>
-  </si>
-  <si>
-    <t>1946[55]</t>
-  </si>
-  <si>
     <t>Australian Antarctic Territory</t>
   </si>
   <si>
     <t>(External Territory of Australia)</t>
   </si>
   <si>
-    <t> Australia</t>
-  </si>
-  <si>
     <t>British Antarctic Territory</t>
   </si>
   <si>
     <t>(British Overseas Territory)</t>
   </si>
   <si>
-    <t> United Kingdom</t>
-  </si>
-  <si>
     <t>Chilean Antarctic Territory</t>
   </si>
   <si>
-    <t> Chile</t>
-  </si>
-  <si>
     <t>(Dependency of Norway)</t>
   </si>
   <si>
-    <t> Norway</t>
-  </si>
-  <si>
     <t>Queen Maud Land</t>
   </si>
   <si>
@@ -90,9 +69,6 @@
     <t>(Dependency of New Zealand)</t>
   </si>
   <si>
-    <t> New Zealand</t>
-  </si>
-  <si>
     <t>Area (km2)</t>
   </si>
   <si>
@@ -136,6 +112,27 @@
   </si>
   <si>
     <t>LONGITUDE</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>Chile</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>New Zealand</t>
   </si>
 </sst>
 </file>
@@ -466,22 +463,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -492,7 +489,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>1840</v>
@@ -501,7 +498,7 @@
         <v>-60</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G2" s="1">
         <v>351000</v>
@@ -509,22 +506,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
+        <v>30</v>
+      </c>
+      <c r="D3">
+        <v>1946</v>
       </c>
       <c r="E3">
         <v>-60</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1">
         <v>1461597</v>
@@ -532,13 +529,13 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D4">
         <v>1933</v>
@@ -547,7 +544,7 @@
         <v>-60</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G4" s="1">
         <v>5896500</v>
@@ -555,13 +552,13 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D5">
         <v>1933</v>
@@ -570,7 +567,7 @@
         <v>-60</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G5" s="1">
         <v>5896500</v>
@@ -578,13 +575,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D6">
         <v>1908</v>
@@ -593,7 +590,7 @@
         <v>-60</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G6" s="1">
         <v>1709400</v>
@@ -601,13 +598,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>1940</v>
@@ -616,7 +613,7 @@
         <v>-60</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G7" s="2">
         <v>1250257.6000000001</v>
@@ -624,13 +621,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D8">
         <v>1939</v>
@@ -639,7 +636,7 @@
         <v>-60</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G8" s="1">
         <v>2700000</v>
@@ -647,13 +644,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D9">
         <v>1923</v>
@@ -662,7 +659,7 @@
         <v>-60</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G9" s="1">
         <v>450000</v>

--- a/js/data/Antarctic_Territorial_Claims_clean.xlsx
+++ b/js/data/Antarctic_Territorial_Claims_clean.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jab14\OneDrive\Documents\GitHub\FIT2179_A2\js\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647BA95E-756C-4B6E-BFDD-27A7DF69A7AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C3F75F-620D-45D3-9F87-E68717905242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4700" yWindow="3110" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -452,13 +452,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="7" max="7" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,11 +477,11 @@
       <c r="F1" t="s">
         <v>28</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -500,11 +500,11 @@
       <c r="F2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>351000</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -523,11 +523,11 @@
       <c r="F3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
         <v>1461597</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -546,11 +546,11 @@
       <c r="F4" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>5896500</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -569,11 +569,11 @@
       <c r="F5" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>5896500</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -592,11 +592,11 @@
       <c r="F6" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>1709400</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -615,11 +615,11 @@
       <c r="F7" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="2">
-        <v>1250257.6000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H7" s="2">
+        <v>1250257</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -638,11 +638,11 @@
       <c r="F8" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>2700000</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -661,7 +661,7 @@
       <c r="F9" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>450000</v>
       </c>
     </row>
